--- a/extenbooks/S1401_extenbook.xlsx
+++ b/extenbooks/S1401_extenbook.xlsx
@@ -5191,7 +5191,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6284,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6311,76 +6311,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nominal GDP Growth and Level of Wage Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1401_research.json", "adequacy_report": "Technical/docs/chapters/CH14_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1401_DPR.md", "epr": "Technical/docs/series/S1401_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1401_load.py", "processor": "Technical/code/P02_processors/P02_S1401_construct.py", "validator": "Technical/code/V03_validators/V03_S1401_validate.py", "processed": "Technical/data/processed/S1401.parquet", "chopped_csv": "Technical/chopped/S1401.csv", "extenbook_xlsx": "Technical/extenbooks/S1401_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:58:43.529185+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1401_extenbook.xlsx
+++ b/extenbooks/S1401_extenbook.xlsx
@@ -1361,7 +1361,7 @@
         <v>2012</v>
       </c>
       <c r="B68" t="n">
-        <v>0.4262404815561983</v>
+        <v>0.5270958418158763</v>
       </c>
       <c r="C68" t="n">
         <v>0.04193905382477081</v>
@@ -1372,7 +1372,7 @@
         <v>2013</v>
       </c>
       <c r="B69" t="n">
-        <v>0.4214284457566083</v>
+        <v>0.523379296915889</v>
       </c>
       <c r="C69" t="n">
         <v>0.03855753394401495</v>
@@ -1383,7 +1383,7 @@
         <v>2014</v>
       </c>
       <c r="B70" t="n">
-        <v>0.4245934465075183</v>
+        <v>0.5253366369572979</v>
       </c>
       <c r="C70" t="n">
         <v>0.04309393168511</v>
@@ -1394,7 +1394,7 @@
         <v>2015</v>
       </c>
       <c r="B71" t="n">
-        <v>0.4295978047358136</v>
+        <v>0.5301661616202749</v>
       </c>
       <c r="C71" t="n">
         <v>0.03900929218069527</v>
@@ -1405,7 +1405,7 @@
         <v>2016</v>
       </c>
       <c r="B72" t="n">
-        <v>0.4302758539749692</v>
+        <v>0.5299732043429289</v>
       </c>
       <c r="C72" t="n">
         <v>0.02787064610318257</v>
@@ -1416,7 +1416,7 @@
         <v>2017</v>
       </c>
       <c r="B73" t="n">
-        <v>0.4321005248646716</v>
+        <v>0.5315289237467292</v>
       </c>
       <c r="C73" t="n">
         <v>0.04292442086809967</v>
@@ -1427,7 +1427,7 @@
         <v>2018</v>
       </c>
       <c r="B74" t="n">
-        <v>0.4308470992881858</v>
+        <v>0.5304573142924973</v>
       </c>
       <c r="C74" t="n">
         <v>0.05325349351877251</v>
@@ -1438,7 +1438,7 @@
         <v>2019</v>
       </c>
       <c r="B75" t="n">
-        <v>0.4329205103328313</v>
+        <v>0.5314117718389922</v>
       </c>
       <c r="C75" t="n">
         <v>0.0427693614934872</v>
@@ -1449,7 +1449,7 @@
         <v>2020</v>
       </c>
       <c r="B76" t="n">
-        <v>0.4428198888791268</v>
+        <v>0.5425986894582256</v>
       </c>
       <c r="C76" t="n">
         <v>-0.007646245943938146</v>
@@ -1460,7 +1460,7 @@
         <v>2021</v>
       </c>
       <c r="B77" t="n">
-        <v>0.4347616077555907</v>
+        <v>0.529317515738033</v>
       </c>
       <c r="C77" t="n">
         <v>0.1099570990455239</v>
@@ -1471,7 +1471,7 @@
         <v>2022</v>
       </c>
       <c r="B78" t="n">
-        <v>0.4269032732551708</v>
+        <v>0.5159700312581871</v>
       </c>
       <c r="C78" t="n">
         <v>0.09816246942232887</v>
@@ -1482,7 +1482,7 @@
         <v>2023</v>
       </c>
       <c r="B79" t="n">
-        <v>0.4218540110559234</v>
+        <v>0.5108459204149129</v>
       </c>
       <c r="C79" t="n">
         <v>0.06743154974393395</v>
@@ -1493,7 +1493,7 @@
         <v>2024</v>
       </c>
       <c r="B80" t="n">
-        <v>0.4228238959413391</v>
+        <v>0.5129050901847849</v>
       </c>
       <c r="C80" t="n">
         <v>0.05344893628060632</v>
@@ -1504,7 +1504,7 @@
         <v>2025</v>
       </c>
       <c r="B81" t="n">
-        <v>0.4218080177168665</v>
+        <v>0.5112427471220349</v>
       </c>
       <c r="C81" t="n">
         <v>0.04997219436007483</v>
@@ -3024,7 +3024,7 @@
         <v>2012</v>
       </c>
       <c r="B151" t="n">
-        <v>0.4262404815561983</v>
+        <v>0.5270958418158763</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>2013</v>
       </c>
       <c r="B152" t="n">
-        <v>0.4214284457566083</v>
+        <v>0.523379296915889</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>2014</v>
       </c>
       <c r="B153" t="n">
-        <v>0.4245934465075183</v>
+        <v>0.5253366369572979</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>2015</v>
       </c>
       <c r="B154" t="n">
-        <v>0.4295978047358136</v>
+        <v>0.5301661616202749</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>2016</v>
       </c>
       <c r="B155" t="n">
-        <v>0.4302758539749692</v>
+        <v>0.5299732043429289</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>2017</v>
       </c>
       <c r="B156" t="n">
-        <v>0.4321005248646716</v>
+        <v>0.5315289237467292</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>2018</v>
       </c>
       <c r="B157" t="n">
-        <v>0.4308470992881858</v>
+        <v>0.5304573142924973</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>2019</v>
       </c>
       <c r="B158" t="n">
-        <v>0.4329205103328313</v>
+        <v>0.5314117718389922</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>2020</v>
       </c>
       <c r="B159" t="n">
-        <v>0.4428198888791268</v>
+        <v>0.5425986894582256</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>2021</v>
       </c>
       <c r="B160" t="n">
-        <v>0.4347616077555907</v>
+        <v>0.529317515738033</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>2022</v>
       </c>
       <c r="B161" t="n">
-        <v>0.4269032732551708</v>
+        <v>0.5159700312581871</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>2023</v>
       </c>
       <c r="B162" t="n">
-        <v>0.4218540110559234</v>
+        <v>0.5108459204149129</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>2024</v>
       </c>
       <c r="B163" t="n">
-        <v>0.4228238959413391</v>
+        <v>0.5129050901847849</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>2025</v>
       </c>
       <c r="B164" t="n">
-        <v>0.4218080177168665</v>
+        <v>0.5112427471220349</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A136"/>
+  <dimension ref="A1:A153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -5156,14 +5156,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record**</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch14</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Subsource registry: `Technical/SUBSOURCE_METADATA.json` -&gt; `SHAIKH_APPENDIX_14_3`, `FRED_GDP`, `FRED_A576RC1`</t>
+          <t>- Subsource registry: `Technical/SUBSOURCE_METADATA.json` -&gt; `SHAIKH_APPENDIX_14_3`, `FRED_GDP`, `FRED_W209RC1`</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>**S1401** is the joint annual time series of (a) the **U.S. wage share** (Compensation of Employees divided by nominal GDP, decimal ratio) and (b) the **nominal GDP growth rate** (annual decimal). Both are plotted as the two axes of Shaikh (2016) Figure 14.10 over 1948-2011, alongside their HP(100)-filtered trends.</t>
+          <t>**S1401** is the joint annual time series of (a) the **U.S. wage share** (Compensation of Employees divided by nominal GDP, decimal ratio) and (b) the **nominal GDP growth rate** (annual decimal). Both are plotted as the two axes of Shaikh (2016) Figure 14.10 over 1948-2011, alongside their HP(100)-filtered trends (Hodrick-Prescott filter, smoothing parameter lambda=100).</t>
         </is>
       </c>
     </row>
@@ -5327,52 +5327,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1401-A, S1401-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S1401-A** wage share | 1948-2011 | Shaikh (2016) Appendix 14.3 `wagesh` column (derived EC/GDP from BEA NIPA T1.10) | decimal ratio | Salvaged `Appendix14_InflationULdata.xlsx` |</t>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| **S1401-B** nominal GDP growth | 1949-2011 (1948 NaN; first-difference) | Shaikh (2016) Appendix 14.3 `ggdp` column | decimal annual rate | Same workbook |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| **S1401-C** nominal GDP (extension) | 1948-2024 | FRED `GDP` (annual avg of quarterly, billions USD SAAR) | billions USD SAAR | Live API |</t>
+          <t>| **S1401-A** wage share | 1948-2011 | Shaikh (2016) Appendix 14.3 `wagesh` column (derived EC/GDP from the U.S. Bureau of Economic Analysis National Income and Product Accounts (NIPA) T1.10) | decimal ratio | Salvaged `Appendix14_InflationULdata.xlsx` |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| **S1401-D** Compensation of Employees, paid (extension) | 1948-2024 | FRED `A576RC1` (annual, billions USD) | billions USD | Live API |</t>
+          <t>| **S1401-B** nominal GDP growth | 1949-2011 (1948 NaN; first-difference) | Shaikh (2016) Appendix 14.3 `ggdp` column | decimal annual rate | Same workbook |</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>| **S1401-C** nominal GDP (extension) | 1948-2024 | FRED `GDP` (annual avg of quarterly, billions USD seasonally adjusted annual rate (SAAR)) | billions USD SAAR | Live API |</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| **S1401-D** Compensation of Employees (extension) | 1948-2025 | FRED `W209RC1` (total compensation = wages, salaries AND employer supplements; NIPA T1.10 line 2; annual, billions USD) | billions USD | Live API |</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S1401 is a **composite**: two derived annual time series sharing a common pair of NIPA Table 1.10 inputs.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -5392,52 +5392,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>**Formula** (verbatim, Appendix 14.2 p. 892):</t>
+          <t>S1401 is a **composite**: two derived annual time series sharing a common pair of NIPA Table 1.10 inputs.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wage_share_t       = EC_t / GDP_t           # decimal ratio</t>
+          <t>**Formula** (verbatim, Appendix 14.2 p. 892):</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nominal_growth_t   = (GDP_t / GDP_{t-1}) - 1   # decimal annual growth rate</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>wage_share_t       = EC_t / GDP_t           # decimal ratio</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>where `EC` = NIPA T1.10 line 2 (Compensation of employees, paid) and `GDP` = NIPA T1.10 line 1.</t>
+          <t>nominal_growth_t   = (GDP_t / GDP_{t-1}) - 1   # decimal annual growth rate</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>The processor (`P02_S1401_construct.py`) emits the Appendix-14.3 values verbatim for 1948-2011, then re-derives the same two formulas from FRED `A576RC1` and `GDP` for 2012+ and concatenates.</t>
+          <t>where `EC` = NIPA T1.10 line 2 (total Compensation of employees) and `GDP` = NIPA T1.10 line 1.</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>The processing step emits the Appendix-14.3 values verbatim for 1948-2011, then re-derives the same two formulas from FRED `W209RC1` (total Compensation of Employees, T1.10 line 2 — the SAME series S1403 uses) and `GDP` for 2012+ and concatenates. **Note (T1.1 remediation, 2026-07-01):** the extension numerator was corrected from `A576RC1` (Wage &amp; Salary Disbursements only, NIPA T2.1, ~20% low) to `W209RC1`; the former produced a spurious -22.2% break at the 2011-&gt;2012 splice.</t>
         </is>
       </c>
     </row>
@@ -5457,31 +5457,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- Book period: 1948-2011 (wagesh: 64 obs; ggdp: 63 obs, 1949-2011)</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>- Extension: 2012-2024 via FRED re-derivation (annual GDP and A576RC1, both available)</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>- Total: 1948-2024</t>
+          <t>- Book period: 1948-2011 (wagesh: 64 obs; ggdp: 63 obs, 1949-2011)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>- Extension: 2012-2025 via FRED re-derivation (annual GDP and W209RC1, both available)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- Total: 1948-2025</t>
         </is>
       </c>
     </row>
@@ -5491,31 +5491,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- Wage share: decimal ratio (e.g., 0.526 in 1948 → 52.6%)</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>- Nominal GDP growth: decimal annual rate (e.g., 0.102 in 1950 → +10.2%)</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- HP(100) trends (separate plotting layer, not in the processed parquet) carry the same units.</t>
+          <t>- Wage share: decimal ratio (e.g., 0.526 in 1948 → 52.6%)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>- Nominal GDP growth: decimal annual rate (e.g., 0.102 in 1950 → +10.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>- HP(100) trends (separate plotting layer, not in the processed parquet) carry the same units.</t>
         </is>
       </c>
     </row>
@@ -5525,214 +5525,210 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1. **Vintage drift**: BEA periodically revises NIPA. Replication should freeze a vintage via FRED ALFRED snapshot. We use the current FRED vintage in this build.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2. **Frequency mismatch**: FRED `GDP` is quarterly SAAR; we use FRED's annual aggregation (avg of 4 quarters) which matches Shaikh's annual-frequency convention.</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3. **Composite, not direct**: the wage share is constructed inside the loader (Appendix 14.3 publishes the derived ratio); for the extension we must hold to Shaikh's exact ratio definition (no proxy substitution allowed).</t>
+          <t>1. **Vintage drift**: BEA periodically revises NIPA. Replication should freeze a vintage via FRED ALFRED snapshot. We use the current FRED vintage in this build.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2. **Frequency mismatch**: FRED `GDP` is quarterly SAAR; we use FRED's annual aggregation (avg of 4 quarters) which matches Shaikh's annual-frequency convention.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **Composite, not direct**: the wage share is constructed inside the loader (Appendix 14.3 publishes the derived ratio); for the extension we must hold to Shaikh's exact ratio definition (no proxy substitution allowed).</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4. **T1.10 vs T2.1 citation nuance**: FRED publishes `W209RC1` under the label "Compensation of employees, received" (NIPA Table 2.1). Shaikh's Appendix 14.2 cites "Compensation of employees, paid" from NIPA Table 1.10 line 2. These are the same total-compensation aggregate (total wages &amp; salaries + employer supplements) and coincide in NIPA accounting; the T2.1-vs-T1.10 difference is one of presentation (received vs paid side of the account), not magnitude. (Clarified 2026-07-01.)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>- CD legacy ID: `S068`</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- CD2 legacy ID: `S068`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>- Book reference: Shaikh (2016) Ch. 14 pp. 664, 892; Figure 14.10</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- Sibling: S1402 (unemployment intensity, the x-axis of Section V's Phillips curves)</t>
+          <t>- Predecessor-build ID: `S068`</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- Predecessor-build ID (second build): `S068`</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- Book reference: Shaikh (2016) Ch. 14 pp. 664, 892; Figure 14.10</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- Sibling: S1402 (unemployment intensity, the x-axis of Section V's Phillips curves)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>- Tolerance: ±1.0% per year on overlap 1948-2011.</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>- Expected MAE vs Appendix 14.3 `wagesh`, `ggdp`: ~0 (pass-through).</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>- Phase 5 hard gate satisfied.</t>
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>- Tolerance: ±1.0% per year on overlap 1948-2011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>- Expected mean absolute error (MAE) vs Appendix 14.3 `wagesh`, `ggdp`: ~0 (pass-through).</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>- Ingestion validation gate satisfied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4">
         <f>== EPR: S1401_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t># S1401 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>**Series**: S1401 (Nominal GDP Growth and Level of Wage Share)</t>
-        </is>
-      </c>
-    </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Chapter**: 14</t>
+          <t># S1401 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>**Series**: S1401 (Nominal GDP Growth and Level of Wage Share)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>## Classification</t>
+          <t>**Chapter**: 14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>- `content_type: time_series`</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>- `construction: composite`</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>- Extension applies (both subseries are composites of live BEA NIPA inputs available via FRED).</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- `content_type: time_series`</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>## Method</t>
+          <t>- `construction: composite`</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>**Re-derivation, not splice.** For 2012+ the loader fetches FRED `GDP` and `A576RC1`</t>
+          <t>- Extension applies (both subseries are composites of live U.S. Bureau of Economic Analysis National Income and Product Accounts (NIPA) inputs available via FRED).</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>annually and applies Shaikh's exact formulas:</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>## Method</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>**Re-derivation, not splice.** For 2012+ the loader fetches FRED `GDP` and `W209RC1`</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>wagesh_t = A576RC1_t / GDP_t</t>
+          <t>annually and applies Shaikh's exact formulas:</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ggdp_t   = GDP_t / GDP_{t-1} - 1</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5742,50 +5738,54 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>wagesh_t = W209RC1_t / GDP_t</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Re-derivation (not growth-rate splice) is mandatory here because wage share is a</t>
+          <t>ggdp_t   = GDP_t / GDP_{t-1} - 1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ratio of two non-stationary aggregates; a lazy splice on the ratio would freeze a</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2011 numerator/denominator coupling that drifts in reality.</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>`W209RC1` is **total** Compensation of Employees (NIPA Table 1.10, line 2 — wages,</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>## Worked example</t>
+          <t>salaries AND employer supplements), the SAME series S1403 uses at quarterly</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024: FRED GDP = 28,832.4 (billions USD SAAR, annual avg); FRED A576RC1 = 15,108.5</t>
+          <t>frequency. A concept guard in the loader now</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>(annual). Therefore wage share 2024 ≈ 0.5240; ggdp 2024 = (28,832.4/27,360.9) - 1 ≈ 0.0538.</t>
+          <t>rejects any wage-and-salary-only substitute at load time.</t>
         </is>
       </c>
     </row>
@@ -5795,35 +5795,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>## No-Proxy disclosure</t>
+          <t>**Prior-defect note (T1.1 remediation, 2026-07-01):** the loader previously fetched</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>**No proxies used.** Both extension subseries are the EXACT BEA NIPA Table 1.10</t>
+          <t>`A576RC1` (Compensation of Employees, Received: Wage &amp; Salary Disbursements — NIPA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>series Shaikh used (compensation of employees, paid; gross domestic product),</t>
+          <t>T2.1, ~20% low because it omits employer supplements). That understated the extension</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>delivered through FRED's BEA mirror. No PPI-for-CPI, no earnings-for-compensation</t>
+          <t>wage share (2012 ≈ 0.426 instead of ≈ 0.527) and produced a spurious -22.2% downward</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>type substitutions.</t>
+          <t>break at the 2011-&gt;2012 splice. Corrected to `W209RC1`.</t>
         </is>
       </c>
     </row>
@@ -5833,95 +5833,202 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>## No-Synthetic disclosure</t>
+          <t>Re-derivation (not growth-rate splice) is mandatory here because wage share is a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>**No synthetic, estimated, placeholder, frozen, or interpolated values.** Every</t>
+          <t>ratio of two non-stationary aggregates; a lazy splice on the ratio would freeze a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>year 1948-2024 traces to a primary BEA observation (book period via</t>
+          <t>2011 numerator/denominator coupling that drifts in reality.</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Appendix 14.3, extension via FRED API).</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>## Worked example</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>## Failure-mode table</t>
+          <t>2024 (current FRED vintage): FRED GDP = 29,298.0 (billions USD seasonally adjusted annual rate (SAAR), annual avg);</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>| Mode | Trigger | Behaviour | Mitigation |</t>
+          <t>FRED W209RC1 = 15,027.1 (annual). Therefore wage share 2024 = 15,027.1 / 29,298.0 ≈</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>0.5129; ggdp 2024 = (29,298.0 / 27,811.5) - 1 ≈ 0.0534. (Numbers drift ~1% with each</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>| `FRED_API_KEY` missing | env var unset | extension skipped; book period only | Phase 5 returns degraded status; CSV/Excel still published |</t>
+          <t>BEA NIPA vintage; freeze an ALFRED snapshot for exact reproduction.)</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>| FRED API outage | `ApiUnavailable` raised | extension skipped | Same as above |</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>| BEA NIPA vintage revision | future re-fetch returns different numbers | values shift within ~1%; documented in EPR | Freeze ALFRED snapshot in production |</t>
+          <t>## No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>**No proxies used.** Both extension subseries are the EXACT BEA NIPA Table 1.10</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>## CD2 divergence pre-disclosure</t>
+          <t>series Shaikh used (total compensation of employees = line 2, W209RC1; gross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>None expected. CD2's S068 used the same BEA inputs but a different vintage; small</t>
+          <t>domestic product = line 1, GDP), delivered through FRED's BEA mirror. No</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
+        <is>
+          <t>PPI-for-CPI, no earnings-for-compensation, no wage-and-salary-for-total-compensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>type substitutions (the last was exactly the A576RC1 defect the T1.1 remediation removed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>## No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>**No synthetic, estimated, placeholder, frozen, or interpolated values.** Every</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>year 1948-2025 traces to a primary BEA observation (book period via</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Appendix 14.3, extension via FRED API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>## Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>| Mode | Trigger | Behaviour | Mitigation |</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>| `FRED_API_KEY` missing | env var unset | extension skipped; book period only | the ingestion step returns degraded status; CSV/Excel still published |</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>| FRED API outage | `ApiUnavailable` raised | extension skipped | Same as above |</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>| BEA NIPA vintage revision | future re-fetch returns different numbers | values shift within ~1%; documented in the Extension Provenance Record | Freeze ALFRED snapshot in production |</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>## Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>None expected. The predecessor build's S068 used the same BEA inputs but a different vintage; small</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>(&lt;1%) divergence is normal. The validator records this as informational.</t>
         </is>
@@ -6269,7 +6376,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:18:16.553653+00:00</t>
+          <t>2026-07-02T11:14:03.371541+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1401_extenbook.xlsx
+++ b/extenbooks/S1401_extenbook.xlsx
@@ -5191,7 +5191,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T11:14:03.371541+00:00</t>
+          <t>2026-07-11T03:44:22.837499+00:00</t>
         </is>
       </c>
     </row>
@@ -6391,11 +6391,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6418,6 +6418,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_14_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.14 Figure 14.10 (Nominal GDP Growth and Level of Wages Share, United States, 1948-2011). Real data present in chopped CSV (155 points, 1948-2025); book_period_validated; chapter title, figure number, and book quotes all KB-verified against ch14_wages_unemployment.md (Fig 14.10 quote verbatim at KB line 1389; source method at Appendix 14.2 KB ch18). Two subseries: wage share (decimal ratio) and nominal GDP growth (decimal annual rate) -- a genuine per-subseries unit split, but NOT flagged MIXED_UNITS because the registry units field is a descriptive composite rather than a banned mixed_* string.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1401_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1401_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Composite of two derived series. Phase 5 hard gate: cell-by-cell validation against Appendix 14.3 wagesh and ggdp before splicing extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_ratio_and_decimal_growth_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
